--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260731.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>598,060,000</t>
+          <t>599,260,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.40%</t>
+          <t>14.47%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>670,290,000</t>
+          <t>671,710,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>12.39%</t>
+          <t>12.67%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.97%</t>
+          <t>10.79%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>9.71%</t>
+          <t>9.70%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.67%</t>
+          <t>7.95%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>5.28%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>4.50%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,760</t>
+          <t>1,724</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -924,95 +924,95 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>209,210,000</t>
+          <t>64,710,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>64,710,000</t>
+          <t>209,210,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>70,789,000</t>
+          <t>25,640,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>遠雄</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>25,640,000</t>
+          <t>70,789,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>77,870,000</t>
+          <t>78,320,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>8,504,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>8,504,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1254,95 +1254,95 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>15,470,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,250,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>15,470,000</t>
+          <t>14,250,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,867,509,726</t>
+          <t>4,791,036,572</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,419,667,572</t>
+          <t>2,390,478,460</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>-1,611,998,997</t>
+          <t>-1,174,697,216</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
